--- a/uploads/voucher_order_CG-202608-0002.xlsx
+++ b/uploads/voucher_order_CG-202608-0002.xlsx
@@ -28,15 +28,15 @@
     <font>
       <name val="宋体"/>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -62,32 +62,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,160 +454,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>采购订单</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>CG-202608-0002</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+          <t>采 购 订 单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>订单编号：CG-202608-0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>供应商</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>甲商</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>交易模式</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>货到付款</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>需求部门</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>后勤类</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>温丽</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>下单日期</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>目标到货日</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>待审批</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>订单金额</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>¥4,500.00</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>目标到货日</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>待审批</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>三方询价选中: 甲商 报价¥4500.00; 联系人: 张三; 电话: 13800000001; 交期/备注: 交期7天, 货到付款; 询价单号: XJ-202608-0002</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>询价/备注</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>三方询价选中: 甲商 报价¥4500.00; 联系人: 张三; 电话: 13800000001; 交期/备注: 交期7天, 货到付款; 询价单号: XJ-202</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>商品明细</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>经手人：                验收人：                审批人：</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>物资名称</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>规格型号</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>单价(元)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>税率%</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>金额(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>采购经办人：                        部门负责人：</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
+  <mergeCells count="16">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A14:H15"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>